--- a/NECP Scenario/Results/Regional Results/EL65_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL65_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176539597641967E-11</v>
+        <v>1.737116458712626E-11</v>
       </c>
       <c r="C2">
-        <v>6.160910073951527E-12</v>
+        <v>9.096365565215811E-12</v>
       </c>
       <c r="D2">
-        <v>9.052355125661779E-12</v>
+        <v>1.336547300642018E-11</v>
       </c>
       <c r="E2">
-        <v>1.330098369341692E-11</v>
+        <v>1.96384018773209E-11</v>
       </c>
       <c r="F2">
-        <v>1.954358241634416E-11</v>
+        <v>2.885534427151006E-11</v>
       </c>
       <c r="G2">
-        <v>2.871587361095107E-11</v>
+        <v>4.239787452774328E-11</v>
       </c>
       <c r="H2">
-        <v>1.740400585200244E-10</v>
+        <v>2.569636485852666E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.556060495142199E-08</v>
+        <v>3.768303912312591E-08</v>
       </c>
       <c r="C3">
-        <v>2.566661346519435E-08</v>
+        <v>3.783330120655338E-08</v>
       </c>
       <c r="D3">
-        <v>5.607479531872712E-08</v>
+        <v>8.253066136914768E-08</v>
       </c>
       <c r="E3">
-        <v>1.124772618414161E-07</v>
+        <v>1.576924480626553E-07</v>
       </c>
       <c r="F3">
-        <v>3.533121748210548E-07</v>
+        <v>4.953664383627973E-07</v>
       </c>
       <c r="G3">
-        <v>3.022674509726129E-06</v>
+        <v>0.009682063173188701</v>
       </c>
       <c r="H3">
-        <v>0.7284481793938758</v>
+        <v>0.5855006088504217</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0378151814484008</v>
+        <v>0.0378145884887367</v>
       </c>
       <c r="D4">
-        <v>0.0378151814681743</v>
+        <v>0.0378145885209938</v>
       </c>
       <c r="E4">
-        <v>0.041527974618475</v>
+        <v>0.0413104238011103</v>
       </c>
       <c r="F4">
-        <v>0.0447503520682613</v>
+        <v>0.0448550295140533</v>
       </c>
       <c r="G4">
-        <v>0.0477415618486992</v>
+        <v>0.0477579707408928</v>
       </c>
       <c r="H4">
-        <v>0.0519746423263037</v>
+        <v>0.0524106730598009</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.52004861721333E-08</v>
+        <v>2.212876861802233E-08</v>
       </c>
       <c r="D9">
-        <v>1.731654602370741E-08</v>
+        <v>2.606437425357325E-08</v>
       </c>
       <c r="E9">
-        <v>1.791494231967634E-08</v>
+        <v>2.659739792780446E-08</v>
       </c>
       <c r="F9">
-        <v>1.79408404962832E-08</v>
+        <v>2.663404473495091E-08</v>
       </c>
       <c r="G9">
-        <v>1.798613523009222E-08</v>
+        <v>2.66990699001639E-08</v>
       </c>
       <c r="H9">
-        <v>1.286100279635458E-07</v>
+        <v>1.951645367123489E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.432901700004365</v>
+        <v>1.432901700004925</v>
       </c>
       <c r="C13">
-        <v>1.432901700006094</v>
+        <v>1.432901700007465</v>
       </c>
       <c r="D13">
-        <v>1.432901700010897</v>
+        <v>1.432901700012325</v>
       </c>
       <c r="E13">
-        <v>1.432901700017789</v>
+        <v>1.432901700022315</v>
       </c>
       <c r="F13">
-        <v>1.432901700032012</v>
+        <v>1.432901700040098</v>
       </c>
       <c r="G13">
-        <v>1.432901700057925</v>
+        <v>1.432901700074685</v>
       </c>
       <c r="H13">
-        <v>1.432901700343359</v>
+        <v>1.432901700403644</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.823814164412111E-08</v>
+        <v>2.684122919283104E-08</v>
       </c>
       <c r="C18">
-        <v>1.824994184403383E-08</v>
+        <v>2.685864266921475E-08</v>
       </c>
       <c r="D18">
-        <v>3.433505102497484E-08</v>
+        <v>5.114590283213576E-08</v>
       </c>
       <c r="E18">
-        <v>7.335340995248313E-08</v>
+        <v>1.064876743354784E-07</v>
       </c>
       <c r="F18">
-        <v>2.009963230620931E-07</v>
+        <v>2.933028684524009E-07</v>
       </c>
       <c r="G18">
-        <v>3.657763611273328E-07</v>
+        <v>6.30441911837074E-07</v>
       </c>
       <c r="H18">
-        <v>3.70081831621654E-06</v>
+        <v>7.623097080400244E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1.096958005494249E-08</v>
+        <v>1.608934367042777E-08</v>
       </c>
       <c r="D19">
-        <v>1.573399657654289E-08</v>
+        <v>2.387480289006921E-08</v>
       </c>
       <c r="E19">
-        <v>3.521205611213682E-08</v>
+        <v>5.241419436680752E-08</v>
       </c>
       <c r="F19">
-        <v>1.15620509105338E-07</v>
+        <v>1.775734496486608E-07</v>
       </c>
       <c r="G19">
-        <v>4.987542449653149E-07</v>
+        <v>1.05613052145717E-06</v>
       </c>
       <c r="H19">
-        <v>0.0426791278192328</v>
+        <v>0.0426791277914413</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.417135178942523E-08</v>
+        <v>3.568835213411154E-08</v>
       </c>
       <c r="C22">
-        <v>2.419991391269796E-08</v>
+        <v>3.573042469754462E-08</v>
       </c>
       <c r="D22">
-        <v>2.713625813599266E-08</v>
+        <v>4.013214968576629E-08</v>
       </c>
       <c r="E22">
-        <v>3.936046150760402E-08</v>
+        <v>5.814696072754655E-08</v>
       </c>
       <c r="F22">
-        <v>5.524107218093249E-08</v>
+        <v>8.158801816281196E-08</v>
       </c>
       <c r="G22">
-        <v>7.884917955320744E-08</v>
+        <v>1.164126578885359E-07</v>
       </c>
       <c r="H22">
-        <v>5.156653751994841E-07</v>
+        <v>7.681007977581648E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>5.409002012500834E-09</v>
+        <v>7.939827583651185E-09</v>
       </c>
       <c r="D24">
-        <v>1.892935249761245E-08</v>
+        <v>2.800794801892083E-08</v>
       </c>
       <c r="E24">
-        <v>6.2824520817532E-08</v>
+        <v>8.945994369413495E-08</v>
       </c>
       <c r="F24">
-        <v>2.17597748765832E-07</v>
+        <v>2.906578201149041E-07</v>
       </c>
       <c r="G24">
-        <v>9.029693914245852E-07</v>
+        <v>1.133272268143815E-06</v>
       </c>
       <c r="H24">
-        <v>0.6722243911321178</v>
+        <v>0.7921002139762786</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.2779842864052153</v>
+        <v>0.1529869494158224</v>
       </c>
       <c r="D27">
-        <v>0.3095360048333025</v>
+        <v>0.2155430693760446</v>
       </c>
       <c r="E27">
-        <v>0.4277226261611785</v>
+        <v>0.2943627307995001</v>
       </c>
       <c r="F27">
-        <v>0.4808108918633088</v>
+        <v>0.3327129858012651</v>
       </c>
       <c r="G27">
-        <v>0.8730162797359782</v>
+        <v>0.7927031798691317</v>
       </c>
       <c r="H27">
-        <v>0.8730162910598086</v>
+        <v>0.7927031847105825</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>8.404012292682556E-09</v>
+        <v>1.241131174628684E-08</v>
       </c>
       <c r="D29">
-        <v>2.639660814263756E-08</v>
+        <v>4.080431279410064E-08</v>
       </c>
       <c r="E29">
-        <v>7.079557857886672E-08</v>
+        <v>1.091882680349195E-07</v>
       </c>
       <c r="F29">
-        <v>2.07411445168766E-07</v>
+        <v>3.376681992539048E-07</v>
       </c>
       <c r="G29">
-        <v>0.1459255121962888</v>
+        <v>0.61746569514382</v>
       </c>
       <c r="H29">
-        <v>0.6174657129378714</v>
+        <v>0.6174657129265319</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>4.789982655866221E-09</v>
+        <v>7.058787762167596E-09</v>
       </c>
       <c r="D31">
-        <v>6.582965182457072E-09</v>
+        <v>9.809844518296764E-09</v>
       </c>
       <c r="E31">
-        <v>1.06148803676278E-08</v>
+        <v>1.573174303019458E-08</v>
       </c>
       <c r="F31">
-        <v>1.594969492397189E-08</v>
+        <v>2.362791333088742E-08</v>
       </c>
       <c r="G31">
-        <v>2.339589361342469E-08</v>
+        <v>3.439467486540563E-08</v>
       </c>
       <c r="H31">
-        <v>1.484214231838067E-07</v>
+        <v>2.264500803277908E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>5.271158085672242E-08</v>
+        <v>7.54426226556301E-08</v>
       </c>
       <c r="D33">
-        <v>5.301703154129037E-08</v>
+        <v>7.615522423339348E-08</v>
       </c>
       <c r="E33">
-        <v>2.362504596133931E-07</v>
+        <v>3.190219386442025E-07</v>
       </c>
       <c r="F33">
-        <v>2.379917492163386E-07</v>
+        <v>3.253674051024123E-07</v>
       </c>
       <c r="G33">
-        <v>2.384517636770124E-07</v>
+        <v>3.262017125954328E-07</v>
       </c>
       <c r="H33">
-        <v>7.731194286833409E-07</v>
+        <v>1.141649053373453E-06</v>
       </c>
     </row>
     <row r="34" spans="1:8">
